--- a/R/Input/DATAccorta.xlsx
+++ b/R/Input/DATAccorta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bancodelarepublica-my.sharepoint.com/personal/ojaulime_banrep_gov_co/Documents/Documents/Research/MP transmission in Colombia/Monetary-Policy-Shocks-and-Central-bank-information-in-Colombia/R/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{61A7BA06-15EE-486E-B896-9040FC5EED2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4087F2B1-D4E3-4715-852B-979993EF0D42}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{61A7BA06-15EE-486E-B896-9040FC5EED2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D3CE402-017D-40F6-AAE4-E63A1AABC26A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5935AB3E-80CE-4E87-9EB4-B18D2E64BDED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5935AB3E-80CE-4E87-9EB4-B18D2E64BDED}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -446,9 +446,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11DADDA8-F05A-4B81-9CDB-818A1AD50DCA}">
   <dimension ref="A1:R181"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -504,7 +504,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>38353</v>
       </c>
@@ -520,6 +520,9 @@
       <c r="E2">
         <v>7.7676703494092711</v>
       </c>
+      <c r="F2">
+        <v>3.2324995238095235</v>
+      </c>
       <c r="G2">
         <v>3.5895238095238098E-2</v>
       </c>
@@ -536,7 +539,7 @@
         <v>4.5591700000000004E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>38384</v>
       </c>
@@ -552,6 +555,9 @@
       <c r="E3">
         <v>7.7581155881396713</v>
       </c>
+      <c r="F3">
+        <v>3.1601249999999999</v>
+      </c>
       <c r="G3">
         <v>3.5740000000000001E-2</v>
       </c>
@@ -568,7 +574,7 @@
         <v>1.36775E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>38412</v>
       </c>
@@ -584,6 +590,9 @@
       <c r="E4">
         <v>7.763748085668702</v>
       </c>
+      <c r="F4">
+        <v>3.5954743478260864</v>
+      </c>
       <c r="G4">
         <v>3.7382608695652172E-2</v>
       </c>
@@ -600,7 +609,7 @@
         <v>0.11486080999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>38443</v>
       </c>
@@ -616,6 +625,9 @@
       <c r="E5">
         <v>7.7621748624483002</v>
       </c>
+      <c r="F5">
+        <v>4.0672619047619047</v>
+      </c>
       <c r="G5">
         <v>4.0985714285714285E-2</v>
       </c>
@@ -632,7 +644,7 @@
         <v>5.4710000000000002E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>38473</v>
       </c>
@@ -648,6 +660,9 @@
       <c r="E6">
         <v>7.7575728194505098</v>
       </c>
+      <c r="F6">
+        <v>3.5778981818181816</v>
+      </c>
       <c r="G6">
         <v>3.7445454545454546E-2</v>
       </c>
@@ -664,7 +679,7 @@
         <v>2.2645E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>38504</v>
       </c>
@@ -680,6 +695,9 @@
       <c r="E7">
         <v>7.7543914919575307</v>
       </c>
+      <c r="F7">
+        <v>3.0278668181818187</v>
+      </c>
       <c r="G7">
         <v>3.393636363636364E-2</v>
       </c>
@@ -696,7 +714,7 @@
         <v>-5.5011599999999997E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>38534</v>
       </c>
@@ -712,6 +730,9 @@
       <c r="E8">
         <v>7.7507783009679514</v>
       </c>
+      <c r="F8">
+        <v>2.8939504761904762</v>
+      </c>
       <c r="G8">
         <v>3.2228571428571426E-2</v>
       </c>
@@ -728,7 +749,7 @@
         <v>-2.826683E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>38565</v>
       </c>
@@ -744,6 +765,9 @@
       <c r="E9">
         <v>7.7433520911902463</v>
       </c>
+      <c r="F9">
+        <v>2.6341447826086961</v>
+      </c>
       <c r="G9">
         <v>3.0447826086956519E-2</v>
       </c>
@@ -760,7 +784,7 @@
         <v>4.5592000000000001E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>38596</v>
       </c>
@@ -776,6 +800,9 @@
       <c r="E10">
         <v>7.7382789502928686</v>
       </c>
+      <c r="F10">
+        <v>2.2312077272727269</v>
+      </c>
       <c r="G10">
         <v>2.6309090909090907E-2</v>
       </c>
@@ -792,7 +819,7 @@
         <v>-0.23819141999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>38626</v>
       </c>
@@ -808,6 +835,9 @@
       <c r="E11">
         <v>7.7374200141435976</v>
       </c>
+      <c r="F11">
+        <v>2.4415671428571426</v>
+      </c>
       <c r="G11">
         <v>2.7761904761904758E-2</v>
       </c>
@@ -824,7 +854,7 @@
         <v>2.860209E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>38657</v>
       </c>
@@ -840,6 +870,9 @@
       <c r="E12">
         <v>7.7318649303105795</v>
       </c>
+      <c r="F12">
+        <v>1.9439195454545457</v>
+      </c>
       <c r="G12">
         <v>2.5350000000000001E-2</v>
       </c>
@@ -856,7 +889,7 @@
         <v>-1.8236699999999999E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>38687</v>
       </c>
@@ -872,6 +905,9 @@
       <c r="E13">
         <v>7.7314525374610676</v>
       </c>
+      <c r="F13">
+        <v>1.6984395454545456</v>
+      </c>
       <c r="G13">
         <v>2.4022727272727272E-2</v>
       </c>
@@ -888,7 +924,7 @@
         <v>3.1914159999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>38718</v>
       </c>
@@ -904,6 +940,9 @@
       <c r="E14">
         <v>7.7291461468609208</v>
       </c>
+      <c r="F14">
+        <v>1.5551886363636362</v>
+      </c>
       <c r="G14">
         <v>2.1427272727272729E-2</v>
       </c>
@@ -920,7 +959,7 @@
         <v>3.1914199999999999E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>38749</v>
       </c>
@@ -936,6 +975,9 @@
       <c r="E15">
         <v>7.7214549899384046</v>
       </c>
+      <c r="F15">
+        <v>1.1658719999999998</v>
+      </c>
       <c r="G15">
         <v>1.7399999999999999E-2</v>
       </c>
@@ -952,7 +994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>38777</v>
       </c>
@@ -968,6 +1010,9 @@
       <c r="E16">
         <v>7.7241637952064925</v>
       </c>
+      <c r="F16">
+        <v>1.259402608695652</v>
+      </c>
       <c r="G16">
         <v>1.6756521739130434E-2</v>
       </c>
@@ -984,7 +1029,7 @@
         <v>5.9269199999999996E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>38808</v>
       </c>
@@ -1000,6 +1045,9 @@
       <c r="E17">
         <v>7.7554630553423074</v>
       </c>
+      <c r="F17">
+        <v>1.3557070000000002</v>
+      </c>
       <c r="G17">
         <v>1.7375000000000002E-2</v>
       </c>
@@ -1016,7 +1064,7 @@
         <v>7.2976819999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>38838</v>
       </c>
@@ -1032,6 +1080,9 @@
       <c r="E18">
         <v>7.7906918955168889</v>
       </c>
+      <c r="F18">
+        <v>1.5364304347826085</v>
+      </c>
       <c r="G18">
         <v>1.8860869565217389E-2</v>
       </c>
@@ -1048,7 +1099,7 @@
         <v>-0.11150349</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>38869</v>
       </c>
@@ -1064,6 +1115,9 @@
       <c r="E19">
         <v>7.8408008611400568</v>
       </c>
+      <c r="F19">
+        <v>1.8483109090909096</v>
+      </c>
       <c r="G19">
         <v>2.313181818181818E-2</v>
       </c>
@@ -1080,7 +1134,7 @@
         <v>1.5440829999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>38899</v>
       </c>
@@ -1096,6 +1150,9 @@
       <c r="E20">
         <v>7.8287310190465513</v>
       </c>
+      <c r="F20">
+        <v>1.6508261904761905</v>
+      </c>
       <c r="G20">
         <v>2.2828571428571427E-2</v>
       </c>
@@ -1112,7 +1169,7 @@
         <v>-9.8828319999999997E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>38930</v>
       </c>
@@ -1128,6 +1185,9 @@
       <c r="E21">
         <v>7.7789021906870133</v>
       </c>
+      <c r="F21">
+        <v>1.3319682608695651</v>
+      </c>
       <c r="G21">
         <v>1.9647826086956522E-2</v>
       </c>
@@ -1144,7 +1204,7 @@
         <v>8.6171700000000004E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>38961</v>
       </c>
@@ -1160,6 +1220,9 @@
       <c r="E22">
         <v>7.7827572407465935</v>
       </c>
+      <c r="F22">
+        <v>1.4092480952380952</v>
+      </c>
       <c r="G22">
         <v>2.0633333333333333E-2</v>
       </c>
@@ -1176,7 +1239,7 @@
         <v>7.2720419999999994E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>38991</v>
       </c>
@@ -1192,6 +1255,9 @@
       <c r="E23">
         <v>7.7682330444370749</v>
       </c>
+      <c r="F23">
+        <v>1.2814281818181816</v>
+      </c>
       <c r="G23">
         <v>1.8104545454545453E-2</v>
       </c>
@@ -1208,7 +1274,7 @@
         <v>5.8236660000000003E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>39022</v>
       </c>
@@ -1224,6 +1290,9 @@
       <c r="E24">
         <v>7.7365079497383782</v>
       </c>
+      <c r="F24">
+        <v>1.196378181818182</v>
+      </c>
       <c r="G24">
         <v>1.8945454545454547E-2</v>
       </c>
@@ -1240,7 +1309,7 @@
         <v>-2.591183E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>39052</v>
       </c>
@@ -1256,6 +1325,9 @@
       <c r="E25">
         <v>7.7237107422044549</v>
       </c>
+      <c r="F25">
+        <v>1.1837133333333332</v>
+      </c>
       <c r="G25">
         <v>1.8109523809523811E-2</v>
       </c>
@@ -1272,7 +1344,7 @@
         <v>0.10091182999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>39083</v>
       </c>
@@ -1288,6 +1360,9 @@
       <c r="E26">
         <v>7.7129177827665556</v>
       </c>
+      <c r="F26">
+        <v>1.1267578260869566</v>
+      </c>
       <c r="G26">
         <v>1.647826086956522E-2</v>
       </c>
@@ -1304,7 +1379,7 @@
         <v>2.305567E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>39114</v>
       </c>
@@ -1320,6 +1395,9 @@
       <c r="E27">
         <v>7.7086935190336998</v>
       </c>
+      <c r="F27">
+        <v>1.0461019999999999</v>
+      </c>
       <c r="G27">
         <v>1.6324999999999999E-2</v>
       </c>
@@ -1336,7 +1414,7 @@
         <v>-0.11212531000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>39142</v>
       </c>
@@ -1352,6 +1430,9 @@
       <c r="E28">
         <v>7.696844258015151</v>
       </c>
+      <c r="F28">
+        <v>1.0707740909090906</v>
+      </c>
       <c r="G28">
         <v>1.7109090909090911E-2</v>
       </c>
@@ -1368,7 +1449,7 @@
         <v>-3.2370080000000002E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>39173</v>
       </c>
@@ -1384,6 +1465,9 @@
       <c r="E29">
         <v>7.6707083337860453</v>
       </c>
+      <c r="F29">
+        <v>0.87178000000000011</v>
+      </c>
       <c r="G29">
         <v>1.4242857142857142E-2</v>
       </c>
@@ -1400,7 +1484,7 @@
         <v>-4.529E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>39203</v>
       </c>
@@ -1416,6 +1500,9 @@
       <c r="E30">
         <v>7.6048496590900099</v>
       </c>
+      <c r="F30">
+        <v>0.83143913043478268</v>
+      </c>
       <c r="G30">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -1432,7 +1519,7 @@
         <v>-0.23709169999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>39234</v>
       </c>
@@ -1448,6 +1535,9 @@
       <c r="E31">
         <v>7.5620368833202152</v>
       </c>
+      <c r="F31">
+        <v>0.75934666666666661</v>
+      </c>
       <c r="G31">
         <v>1.0838095238095239E-2</v>
       </c>
@@ -1464,7 +1554,7 @@
         <v>-5.8933899999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>39264</v>
       </c>
@@ -1480,6 +1570,9 @@
       <c r="E32">
         <v>7.5760307059069119</v>
       </c>
+      <c r="F32">
+        <v>1.0155527272727272</v>
+      </c>
       <c r="G32">
         <v>1.3545454545454546E-2</v>
       </c>
@@ -1496,7 +1589,7 @@
         <v>5.5911830000000003E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>39295</v>
       </c>
@@ -1512,6 +1605,9 @@
       <c r="E33">
         <v>7.6296259615612003</v>
       </c>
+      <c r="F33">
+        <v>1.4526878260869562</v>
+      </c>
       <c r="G33">
         <v>1.8643478260869567E-2</v>
       </c>
@@ -1528,7 +1624,7 @@
         <v>-5.674825E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>39326</v>
       </c>
@@ -1544,6 +1640,9 @@
       <c r="E34">
         <v>7.6577788891837795</v>
       </c>
+      <c r="F34">
+        <v>1.3141545000000001</v>
+      </c>
       <c r="G34">
         <v>1.806E-2</v>
       </c>
@@ -1560,7 +1659,7 @@
         <v>-0.23797336999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>39356</v>
       </c>
@@ -1576,6 +1675,9 @@
       <c r="E35">
         <v>7.602531132533902</v>
       </c>
+      <c r="F35">
+        <v>1.1503156521739131</v>
+      </c>
       <c r="G35">
         <v>1.6060869565217392E-2</v>
       </c>
@@ -1592,7 +1694,7 @@
         <v>-0.25985736999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>39387</v>
       </c>
@@ -1608,6 +1710,9 @@
       <c r="E36">
         <v>7.624482258062538</v>
       </c>
+      <c r="F36">
+        <v>1.5001013636363636</v>
+      </c>
       <c r="G36">
         <v>1.9686363636363637E-2</v>
       </c>
@@ -1624,7 +1729,7 @@
         <v>0.11908816999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>39417</v>
       </c>
@@ -1640,6 +1745,9 @@
       <c r="E37">
         <v>7.607978117926308</v>
       </c>
+      <c r="F37">
+        <v>1.2762866666666663</v>
+      </c>
       <c r="G37">
         <v>1.8776190476190478E-2</v>
       </c>
@@ -1656,7 +1764,7 @@
         <v>0.23253254000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>39448</v>
       </c>
@@ -1673,7 +1781,7 @@
         <v>7.5911500590993981</v>
       </c>
       <c r="F38">
-        <v>1.5311818181818189</v>
+        <v>1.7183569565217391</v>
       </c>
       <c r="G38">
         <v>2.3956521739130435E-2</v>
@@ -1712,7 +1820,7 @@
         <v>-4.2562299999999997E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>39479</v>
       </c>
@@ -1729,7 +1837,7 @@
         <v>7.5513287384721055</v>
       </c>
       <c r="F39">
-        <v>1.5715000000000003</v>
+        <v>1.9445685714285719</v>
       </c>
       <c r="G39">
         <v>2.4966666666666665E-2</v>
@@ -1768,7 +1876,7 @@
         <v>5.9226639999999997E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39508</v>
       </c>
@@ -1785,7 +1893,7 @@
         <v>7.5212638368818654</v>
       </c>
       <c r="F40">
-        <v>2.175071428571429</v>
+        <v>2.175211904761905</v>
       </c>
       <c r="G40">
         <v>2.6371428571428573E-2</v>
@@ -1824,7 +1932,7 @@
         <v>0.32610652000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39539</v>
       </c>
@@ -1841,7 +1949,7 @@
         <v>7.4933896293161135</v>
       </c>
       <c r="F41">
-        <v>1.7280909090909098</v>
+        <v>1.7164050000000002</v>
       </c>
       <c r="G41">
         <v>2.157727272727273E-2</v>
@@ -1880,7 +1988,7 @@
         <v>0.36944381999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>39569</v>
       </c>
@@ -1897,7 +2005,7 @@
         <v>7.4832500403549966</v>
       </c>
       <c r="F42">
-        <v>1.5565000000000007</v>
+        <v>1.3361731818181821</v>
       </c>
       <c r="G42">
         <v>1.7904545454545454E-2</v>
@@ -1936,7 +2044,7 @@
         <v>-0.44944381999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>39600</v>
       </c>
@@ -1953,7 +2061,7 @@
         <v>7.4455810947304846</v>
       </c>
       <c r="F43">
-        <v>1.5565000000000004</v>
+        <v>1.329631904761905</v>
       </c>
       <c r="G43">
         <v>1.8061904761904762E-2</v>
@@ -1992,7 +2100,7 @@
         <v>-0.44350611000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>39630</v>
       </c>
@@ -2009,7 +2117,7 @@
         <v>7.4861030933138544</v>
       </c>
       <c r="F44">
-        <v>1.5565000000000007</v>
+        <v>1.5785386956521739</v>
       </c>
       <c r="G44">
         <v>2.1752173913043477E-2</v>
@@ -2048,7 +2156,7 @@
         <v>0.46301308000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>39661</v>
       </c>
@@ -2065,7 +2173,7 @@
         <v>7.5198496585626904</v>
       </c>
       <c r="F45">
-        <v>1.5565000000000004</v>
+        <v>1.5904666666666669</v>
       </c>
       <c r="G45">
         <v>2.2195238095238098E-2</v>
@@ -2104,7 +2212,7 @@
         <v>-4.4953279999999998E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>39692</v>
       </c>
@@ -2121,7 +2229,7 @@
         <v>7.6333890105763809</v>
       </c>
       <c r="F46">
-        <v>1.633455681818182</v>
+        <v>2.0010522727272733</v>
       </c>
       <c r="G46">
         <v>2.7045454545454543E-2</v>
@@ -2160,7 +2268,7 @@
         <v>-6.0536899999999996E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>39722</v>
       </c>
@@ -2177,7 +2285,7 @@
         <v>7.7359445854342237</v>
       </c>
       <c r="F47">
-        <v>3.5578127391304353</v>
+        <v>3.6700208695652177</v>
       </c>
       <c r="G47">
         <v>5.343478260869565E-2</v>
@@ -2216,7 +2324,7 @@
         <v>-0.49770323999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>39753</v>
       </c>
@@ -2233,7 +2341,7 @@
         <v>7.7532629665371235</v>
       </c>
       <c r="F48">
-        <v>3.5303759500000003</v>
+        <v>3.5139074999999997</v>
       </c>
       <c r="G48">
         <v>5.4960000000000002E-2</v>
@@ -2272,7 +2380,7 @@
         <v>-0.38327783999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>39783</v>
       </c>
@@ -2289,7 +2397,7 @@
         <v>7.7198936539695433</v>
       </c>
       <c r="F49">
-        <v>3.4973959130434786</v>
+        <v>3.5219273913043478</v>
       </c>
       <c r="G49">
         <v>5.362608695652174E-2</v>
@@ -2328,7 +2436,7 @@
         <v>0.15606513999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>39814</v>
       </c>
@@ -2345,7 +2453,7 @@
         <v>7.7200090633400249</v>
       </c>
       <c r="F50">
-        <v>3.3825509545454548</v>
+        <v>3.3843295454545452</v>
       </c>
       <c r="G50">
         <v>5.0295454545454546E-2</v>
@@ -2384,7 +2492,7 @@
         <v>-0.47338358000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>39845</v>
       </c>
@@ -2401,7 +2509,7 @@
         <v>7.8295269629586111</v>
       </c>
       <c r="F51">
-        <v>4.3061789499999996</v>
+        <v>4.3331114999999993</v>
       </c>
       <c r="G51">
         <v>4.7774999999999998E-2</v>
@@ -2440,7 +2548,7 @@
         <v>-0.54739097999999997</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>39873</v>
       </c>
@@ -2457,7 +2565,7 @@
         <v>7.8148882058715179</v>
       </c>
       <c r="F52">
-        <v>4.4452824545454543</v>
+        <v>4.3914572727272718</v>
       </c>
       <c r="G52">
         <v>4.8340909090909094E-2</v>
@@ -2496,7 +2604,7 @@
         <v>-0.51314877000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>39904</v>
       </c>
@@ -2513,7 +2621,7 @@
         <v>7.7745868229403738</v>
       </c>
       <c r="F53">
-        <v>3.3008863181818189</v>
+        <v>3.300115454545455</v>
       </c>
       <c r="G53">
         <v>4.1754545454545454E-2</v>
@@ -2552,7 +2660,7 @@
         <v>-0.55107950000000006</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>39934</v>
       </c>
@@ -2569,7 +2677,7 @@
         <v>7.7097344426781342</v>
       </c>
       <c r="F54">
-        <v>2.5014562857142861</v>
+        <v>2.4715309523809528</v>
       </c>
       <c r="G54">
         <v>3.2247619047619046E-2</v>
@@ -2608,7 +2716,7 @@
         <v>-0.50324221000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>39965</v>
       </c>
@@ -2625,7 +2733,7 @@
         <v>7.6449384835316936</v>
       </c>
       <c r="F55">
-        <v>2.1444545454545452</v>
+        <v>2.1541163636363634</v>
       </c>
       <c r="G55">
         <v>2.9754545454545457E-2</v>
@@ -2664,7 +2772,7 @@
         <v>-0.63880201999999997</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>39995</v>
       </c>
@@ -2681,7 +2789,7 @@
         <v>7.626901535410699</v>
       </c>
       <c r="F56">
-        <v>2.0457608695652176</v>
+        <v>2.0090052173913047</v>
       </c>
       <c r="G56">
         <v>2.9760869565217393E-2</v>
@@ -2720,7 +2828,7 @@
         <v>1.3102050000000001E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>40026</v>
       </c>
@@ -2737,7 +2845,7 @@
         <v>7.6103427593614335</v>
       </c>
       <c r="F57">
-        <v>1.5845904761904763</v>
+        <v>1.5896795238095236</v>
       </c>
       <c r="G57">
         <v>2.6114285714285718E-2</v>
@@ -2776,7 +2884,7 @@
         <v>6.4171309999999995E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>40057</v>
       </c>
@@ -2793,7 +2901,7 @@
         <v>7.5912409369797844</v>
       </c>
       <c r="F58">
-        <v>1.5543</v>
+        <v>1.5523713636363636</v>
       </c>
       <c r="G58">
         <v>2.5031818181818183E-2</v>
@@ -2832,7 +2940,7 @@
         <v>-0.24067295</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>40087</v>
       </c>
@@ -2849,7 +2957,7 @@
         <v>7.5521637940465709</v>
       </c>
       <c r="F59">
-        <v>1.5382954545454546</v>
+        <v>1.5501549999999999</v>
       </c>
       <c r="G59">
         <v>2.1836363636363636E-2</v>
@@ -2888,7 +2996,7 @@
         <v>-1.2484429999999999E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>40118</v>
       </c>
@@ -2905,7 +3013,7 @@
         <v>7.5875993644510551</v>
       </c>
       <c r="F60">
-        <v>1.5160428571428575</v>
+        <v>1.514283333333333</v>
       </c>
       <c r="G60">
         <v>2.1333333333333333E-2</v>
@@ -2944,7 +3052,7 @@
         <v>-0.35513646999999998</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>40148</v>
       </c>
@@ -2961,7 +3069,7 @@
         <v>7.6093913269379883</v>
       </c>
       <c r="F61">
-        <v>1.4536130434782608</v>
+        <v>1.456225652173913</v>
       </c>
       <c r="G61">
         <v>2.0813043478260868E-2</v>
@@ -3000,7 +3108,7 @@
         <v>0.12279754</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>40179</v>
       </c>
@@ -3017,7 +3125,7 @@
         <v>7.5899375641923665</v>
       </c>
       <c r="F62">
-        <v>1.4538298571428572</v>
+        <v>1.4524785714285715</v>
       </c>
       <c r="G62">
         <v>2.0971428571428571E-2</v>
@@ -3056,7 +3164,7 @@
         <v>0.11314877</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>40210</v>
       </c>
@@ -3073,7 +3181,7 @@
         <v>7.5770656056857346</v>
       </c>
       <c r="F63">
-        <v>1.6648500500000003</v>
+        <v>1.6563954999999999</v>
       </c>
       <c r="G63">
         <v>2.351E-2</v>
@@ -3112,7 +3220,7 @@
         <v>0.10201721</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>40238</v>
       </c>
@@ -3129,7 +3237,7 @@
         <v>7.5543872058006132</v>
       </c>
       <c r="F64">
-        <v>1.4479916086956524</v>
+        <v>1.4498091304347827</v>
       </c>
       <c r="G64">
         <v>1.89E-2</v>
@@ -3168,7 +3276,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>40269</v>
       </c>
@@ -3185,7 +3293,7 @@
         <v>7.570628801852255</v>
       </c>
       <c r="F65">
-        <v>1.3772437272727274</v>
+        <v>1.3759154545454548</v>
       </c>
       <c r="G65">
         <v>1.7277272727272728E-2</v>
@@ -3224,7 +3332,7 @@
         <v>-0.27829754000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>40299</v>
       </c>
@@ -3241,7 +3349,7 @@
         <v>7.5930517229973686</v>
       </c>
       <c r="F66">
-        <v>1.6470119523809523</v>
+        <v>1.6510447619047619</v>
       </c>
       <c r="G66">
         <v>2.3104761904761902E-2</v>
@@ -3280,7 +3388,7 @@
         <v>-3.0679919999999999E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>40330</v>
       </c>
@@ -3297,7 +3405,7 @@
         <v>7.5631486699301664</v>
       </c>
       <c r="F67">
-        <v>1.5667730454545454</v>
+        <v>1.5695986363636365</v>
       </c>
       <c r="G67">
         <v>2.2304545454545452E-2</v>
@@ -3336,7 +3444,7 @@
         <v>-3.0679919999999999E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>40360</v>
       </c>
@@ -3353,7 +3461,7 @@
         <v>7.5361079056309173</v>
       </c>
       <c r="F68">
-        <v>1.358631818181818</v>
+        <v>1.3556977272727275</v>
       </c>
       <c r="G68">
         <v>1.9904545454545453E-2</v>
@@ -3392,7 +3500,7 @@
         <v>-3.2695490000000001E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>40391</v>
       </c>
@@ -3409,7 +3517,7 @@
         <v>7.5060751631308031</v>
       </c>
       <c r="F69">
-        <v>1.2250727272727273</v>
+        <v>1.2328827272727272</v>
       </c>
       <c r="G69">
         <v>1.6577272727272729E-2</v>
@@ -3448,7 +3556,7 @@
         <v>0.19299957000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>40422</v>
       </c>
@@ -3465,7 +3573,7 @@
         <v>7.4986482255033255</v>
       </c>
       <c r="F70">
-        <v>1.2419681818181816</v>
+        <v>1.246678181818182</v>
       </c>
       <c r="G70">
         <v>1.757727272727273E-2</v>
@@ -3504,7 +3612,7 @@
         <v>-0.15866063999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>40452</v>
       </c>
@@ -3521,7 +3629,7 @@
         <v>7.5002309333703874</v>
       </c>
       <c r="F71">
-        <v>1.0207714095238096</v>
+        <v>1.0197999999999998</v>
       </c>
       <c r="G71">
         <v>1.5814285714285715E-2</v>
@@ -3560,7 +3668,7 @@
         <v>-2.303115E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>40483</v>
       </c>
@@ -3577,7 +3685,7 @@
         <v>7.5303029409457398</v>
       </c>
       <c r="F72">
-        <v>1.0669397999999999</v>
+        <v>1.0676395454545455</v>
       </c>
       <c r="G72">
         <v>1.5163636363636362E-2</v>
@@ -3616,7 +3724,7 @@
         <v>0.11330941</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>40513</v>
       </c>
@@ -3633,7 +3741,7 @@
         <v>7.5631279002041181</v>
       </c>
       <c r="F73">
-        <v>1.1408608695652174</v>
+        <v>1.1371595652173911</v>
       </c>
       <c r="G73">
         <v>1.6073913043478258E-2</v>
@@ -3672,7 +3780,7 @@
         <v>-4.4633199999999998E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>40544</v>
       </c>
@@ -3689,7 +3797,7 @@
         <v>7.5318953022388033</v>
       </c>
       <c r="F74">
-        <v>1.1060576190476192</v>
+        <v>1.1076128571428572</v>
       </c>
       <c r="G74">
         <v>1.4576190476190475E-2</v>
@@ -3728,7 +3836,7 @@
         <v>-2.235123E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>40575</v>
       </c>
@@ -3745,7 +3853,7 @@
         <v>7.5404143909018382</v>
       </c>
       <c r="F75">
-        <v>1.1927110000000001</v>
+        <v>1.1938675000000003</v>
       </c>
       <c r="G75">
         <v>1.5094999999999999E-2</v>
@@ -3784,7 +3892,7 @@
         <v>9.36332E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>40603</v>
       </c>
@@ -3801,7 +3909,7 @@
         <v>7.5413541333116987</v>
       </c>
       <c r="F76">
-        <v>1.164005217391304</v>
+        <v>1.1551730434782608</v>
       </c>
       <c r="G76">
         <v>1.5513043478260869E-2</v>
@@ -3840,7 +3948,7 @@
         <v>0.24520900000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>40634</v>
       </c>
@@ -3857,7 +3965,7 @@
         <v>7.5026113411518107</v>
       </c>
       <c r="F77">
-        <v>1.0239776095238096</v>
+        <v>1.0219452380952379</v>
       </c>
       <c r="G77">
         <v>1.5152380952380952E-2</v>
@@ -3896,7 +4004,7 @@
         <v>2.351557E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>40664</v>
       </c>
@@ -3913,7 +4021,7 @@
         <v>7.4964581906686094</v>
       </c>
       <c r="F78">
-        <v>1.0145068045454544</v>
+        <v>1.010004090909091</v>
       </c>
       <c r="G78">
         <v>1.4759090909090909E-2</v>
@@ -3952,7 +4060,7 @@
         <v>5.9281970000000003E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>40695</v>
       </c>
@@ -3969,7 +4077,7 @@
         <v>7.4857945924293761</v>
       </c>
       <c r="F79">
-        <v>1.0814222681818182</v>
+        <v>1.079760909090909</v>
       </c>
       <c r="G79">
         <v>1.4463636363636363E-2</v>
@@ -4008,7 +4116,7 @@
         <v>6.0484429999999999E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>40725</v>
       </c>
@@ -4025,7 +4133,7 @@
         <v>7.474062912207132</v>
       </c>
       <c r="F80">
-        <v>1.1152638095238097</v>
+        <v>1.1118366666666666</v>
       </c>
       <c r="G80">
         <v>1.4071428571428572E-2</v>
@@ -4064,7 +4172,7 @@
         <v>2.2031149999999999E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>40756</v>
       </c>
@@ -4081,7 +4189,7 @@
         <v>7.4871961029262479</v>
       </c>
       <c r="F81">
-        <v>1.4281439130434783</v>
+        <v>1.437711739130435</v>
       </c>
       <c r="G81">
         <v>1.7082608695652174E-2</v>
@@ -4120,7 +4228,7 @@
         <v>-0.23957581</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>40787</v>
       </c>
@@ -4137,7 +4245,7 @@
         <v>7.515426267189631</v>
       </c>
       <c r="F82">
-        <v>1.7431213636363634</v>
+        <v>1.7437145454545453</v>
       </c>
       <c r="G82">
         <v>2.1481818181818182E-2</v>
@@ -4176,7 +4284,7 @@
         <v>-4.789098E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>40817</v>
       </c>
@@ -4193,7 +4301,7 @@
         <v>7.5550574541317577</v>
       </c>
       <c r="F83">
-        <v>1.6553461904761904</v>
+        <v>1.6776871428571429</v>
       </c>
       <c r="G83">
         <v>2.070952380952381E-2</v>
@@ -4232,7 +4340,7 @@
         <v>-5.9437700000000003E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>40848</v>
       </c>
@@ -4249,7 +4357,7 @@
         <v>7.5591477385009895</v>
       </c>
       <c r="F84">
-        <v>1.6410554545454543</v>
+        <v>1.6676709090909092</v>
       </c>
       <c r="G84">
         <v>1.9704545454545454E-2</v>
@@ -4288,7 +4396,7 @@
         <v>4.510902E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>40878</v>
       </c>
@@ -4305,7 +4413,7 @@
         <v>7.5673870402042649</v>
       </c>
       <c r="F85">
-        <v>1.5082499999999999</v>
+        <v>1.5293718181818183</v>
       </c>
       <c r="G85">
         <v>1.8713636363636363E-2</v>
@@ -4344,7 +4452,7 @@
         <v>-3.4757789999999997E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>40909</v>
       </c>
@@ -4361,7 +4469,7 @@
         <v>7.5240862079234461</v>
       </c>
       <c r="F86">
-        <v>1.4843727272727276</v>
+        <v>1.4868018181818181</v>
       </c>
       <c r="G86">
         <v>1.9713636363636364E-2</v>
@@ -4400,7 +4508,7 @@
         <v>0.11464877</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>40940</v>
       </c>
@@ -4417,7 +4525,7 @@
         <v>7.4863666459488041</v>
       </c>
       <c r="F87">
-        <v>1.2929285714285712</v>
+        <v>1.2951199999999998</v>
       </c>
       <c r="G87">
         <v>1.7557142857142858E-2</v>
@@ -4456,7 +4564,7 @@
         <v>8.6711070000000001E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>40969</v>
       </c>
@@ -4473,7 +4581,7 @@
         <v>7.4766648881145672</v>
       </c>
       <c r="F88">
-        <v>1.1278995454545453</v>
+        <v>1.1281377272727271</v>
       </c>
       <c r="G88">
         <v>1.490909090909091E-2</v>
@@ -4512,7 +4620,7 @@
         <v>-1.2164339999999999E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>41000</v>
       </c>
@@ -4529,7 +4637,7 @@
         <v>7.4815895041551155</v>
       </c>
       <c r="F89">
-        <v>1.1505499999999997</v>
+        <v>1.1546595238095239</v>
       </c>
       <c r="G89">
         <v>1.4747619047619048E-2</v>
@@ -4568,7 +4676,7 @@
         <v>-1.2437699999999999E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>41030</v>
       </c>
@@ -4585,7 +4693,7 @@
         <v>7.4918016242685326</v>
       </c>
       <c r="F90">
-        <v>1.3317521739130436</v>
+        <v>1.3373017391304347</v>
       </c>
       <c r="G90">
         <v>1.7430434782608698E-2</v>
@@ -4624,7 +4732,7 @@
         <v>-0.23711719000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>41061</v>
       </c>
@@ -4641,7 +4749,7 @@
         <v>7.4914390942512599</v>
       </c>
       <c r="F91">
-        <v>1.4706861904761903</v>
+        <v>1.4727947619047617</v>
       </c>
       <c r="G91">
         <v>1.7276190476190476E-2</v>
@@ -4680,7 +4788,7 @@
         <v>-2.275779E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>41091</v>
       </c>
@@ -4697,7 +4805,7 @@
         <v>7.4868543154866902</v>
       </c>
       <c r="F92">
-        <v>1.2870909090909088</v>
+        <v>1.299115</v>
       </c>
       <c r="G92">
         <v>1.5095454545454547E-2</v>
@@ -4736,7 +4844,7 @@
         <v>-0.18792212999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>41122</v>
       </c>
@@ -4753,7 +4861,7 @@
         <v>7.4990579776090387</v>
       </c>
       <c r="F93">
-        <v>1.1412952173913045</v>
+        <v>1.1463843478260869</v>
       </c>
       <c r="G93">
         <v>1.2878260869565219E-2</v>
@@ -4792,7 +4900,7 @@
         <v>-4.3515570000000003E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>41153</v>
       </c>
@@ -4809,7 +4917,7 @@
         <v>7.4973070518309228</v>
       </c>
       <c r="F94">
-        <v>1.0096134900000002</v>
+        <v>1.0130295</v>
       </c>
       <c r="G94">
         <v>1.265E-2</v>
@@ -4848,7 +4956,7 @@
         <v>-8.2380309999999998E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>41183</v>
       </c>
@@ -4865,7 +4973,7 @@
         <v>7.4982992501302439</v>
       </c>
       <c r="F95">
-        <v>1.0236830347826087</v>
+        <v>1.0269830434782612</v>
       </c>
       <c r="G95">
         <v>1.1065217391304349E-2</v>
@@ -4904,7 +5012,7 @@
         <v>1.7195490000000001E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>41214</v>
       </c>
@@ -4921,7 +5029,7 @@
         <v>7.5067511080368075</v>
       </c>
       <c r="F96">
-        <v>1.0057858772727273</v>
+        <v>1.0081536363636365</v>
       </c>
       <c r="G96">
         <v>1.2281818181818182E-2</v>
@@ -4960,7 +5068,7 @@
         <v>-0.22312088999999999</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>41244</v>
       </c>
@@ -4977,7 +5085,7 @@
         <v>7.4921695972433975</v>
       </c>
       <c r="F97">
-        <v>0.94884277619047608</v>
+        <v>0.95919761904761913</v>
       </c>
       <c r="G97">
         <v>1.1614285714285714E-2</v>
@@ -5016,7 +5124,7 @@
         <v>-3.877336E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>41275</v>
       </c>
@@ -5033,7 +5141,7 @@
         <v>7.4787404752694293</v>
       </c>
       <c r="F98">
-        <v>0.93960343478260855</v>
+        <v>0.93505956521739098</v>
       </c>
       <c r="G98">
         <v>1.1243478260869565E-2</v>
@@ -5072,7 +5180,7 @@
         <v>1.8468849999999998E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>41306</v>
       </c>
@@ -5089,7 +5197,7 @@
         <v>7.4907973728534989</v>
       </c>
       <c r="F99">
-        <v>0.9842204699999999</v>
+        <v>0.98625849999999993</v>
       </c>
       <c r="G99">
         <v>1.3130000000000001E-2</v>
@@ -5128,7 +5236,7 @@
         <v>0.12164506999999999</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>41334</v>
       </c>
@@ -5145,7 +5253,7 @@
         <v>7.5010213489324258</v>
       </c>
       <c r="F100">
-        <v>0.9347256428571431</v>
+        <v>0.94501761904761916</v>
       </c>
       <c r="G100">
         <v>1.4180952380952379E-2</v>
@@ -5184,7 +5292,7 @@
         <v>-0.24754302</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>41365</v>
       </c>
@@ -5201,7 +5309,7 @@
         <v>7.5120493876730814</v>
       </c>
       <c r="F101">
-        <v>0.90689674999999992</v>
+        <v>0.90977727272727271</v>
       </c>
       <c r="G101">
         <v>1.3195454545454547E-2</v>
@@ -5240,7 +5348,7 @@
         <v>0.17684753</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>41395</v>
       </c>
@@ -5257,7 +5365,7 @@
         <v>7.5230057808336008</v>
       </c>
       <c r="F102">
-        <v>0.85768296956521739</v>
+        <v>0.85517217391304368</v>
       </c>
       <c r="G102">
         <v>1.3539130434782609E-2</v>
@@ -5296,7 +5404,7 @@
         <v>0.16510695</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>41426</v>
       </c>
@@ -5313,7 +5421,7 @@
         <v>7.5545967066655706</v>
       </c>
       <c r="F103">
-        <v>1.3667230000000001</v>
+        <v>1.3652794999999998</v>
       </c>
       <c r="G103">
         <v>1.7999999999999999E-2</v>
@@ -5352,7 +5460,7 @@
         <v>0.20424875000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>41456</v>
       </c>
@@ -5369,7 +5477,7 @@
         <v>7.5499196432670033</v>
       </c>
       <c r="F104">
-        <v>1.3536463478260874</v>
+        <v>1.3427452173913041</v>
       </c>
       <c r="G104">
         <v>1.6952173913043479E-2</v>
@@ -5408,7 +5516,7 @@
         <v>0.14866925</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>41487</v>
       </c>
@@ -5425,7 +5533,7 @@
         <v>7.5515336279769629</v>
       </c>
       <c r="F105">
-        <v>1.3172954545454545</v>
+        <v>1.3127122727272729</v>
       </c>
       <c r="G105">
         <v>1.8295454545454545E-2</v>
@@ -5464,7 +5572,7 @@
         <v>-0.14827826999999999</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>41518</v>
       </c>
@@ -5481,7 +5589,7 @@
         <v>7.5597679161835272</v>
       </c>
       <c r="F106">
-        <v>1.2541987142857141</v>
+        <v>1.2470399999999999</v>
       </c>
       <c r="G106">
         <v>1.8138095238095238E-2</v>
@@ -5520,7 +5628,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>41548</v>
       </c>
@@ -5537,7 +5645,7 @@
         <v>7.5421657420123474</v>
       </c>
       <c r="F107">
-        <v>1.2478347826086955</v>
+        <v>1.2435973913043481</v>
       </c>
       <c r="G107">
         <v>1.7130434782608697E-2</v>
@@ -5576,7 +5684,7 @@
         <v>1.72664E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>41579</v>
       </c>
@@ -5593,7 +5701,7 @@
         <v>7.561194427668319</v>
       </c>
       <c r="F108">
-        <v>1.2714761904761906</v>
+        <v>1.2810742857142861</v>
       </c>
       <c r="G108">
         <v>1.8314285714285714E-2</v>
@@ -5632,7 +5740,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>41609</v>
       </c>
@@ -5649,7 +5757,7 @@
         <v>7.5673870402042649</v>
       </c>
       <c r="F109">
-        <v>1.1973090909090909</v>
+        <v>1.2082036363636364</v>
       </c>
       <c r="G109">
         <v>1.770909090909091E-2</v>
@@ -5688,7 +5796,7 @@
         <v>9.9688499999999996E-3</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>41640</v>
       </c>
@@ -5705,7 +5813,7 @@
         <v>7.5809089140221788</v>
       </c>
       <c r="F110">
-        <v>1.2387782608695652</v>
+        <v>1.243285217391304</v>
       </c>
       <c r="G110">
         <v>1.8208695652173913E-2</v>
@@ -5744,7 +5852,7 @@
         <v>-5.3045100000000001E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>41671</v>
       </c>
@@ -5761,7 +5869,7 @@
         <v>7.6209550555934698</v>
       </c>
       <c r="F111">
-        <v>1.19618</v>
+        <v>1.2010255000000001</v>
       </c>
       <c r="G111">
         <v>1.8825000000000001E-2</v>
@@ -5800,7 +5908,7 @@
         <v>-3.9844299999999997E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>41699</v>
       </c>
@@ -5817,7 +5925,7 @@
         <v>7.6119363615357845</v>
       </c>
       <c r="F112">
-        <v>1.1087095238095239</v>
+        <v>1.1057257142857142</v>
       </c>
       <c r="G112">
         <v>1.7676190476190477E-2</v>
@@ -5856,7 +5964,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>41730</v>
       </c>
@@ -5873,7 +5981,7 @@
         <v>7.5700668925832373</v>
       </c>
       <c r="F113">
-        <v>1.0083408863636363</v>
+        <v>1.0078663636363641</v>
       </c>
       <c r="G113">
         <v>1.6154545454545453E-2</v>
@@ -5912,7 +6020,7 @@
         <v>0.12378893000000001</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>41760</v>
       </c>
@@ -5929,7 +6037,7 @@
         <v>7.5577130816464981</v>
       </c>
       <c r="F114">
-        <v>0.89018174090909075</v>
+        <v>0.89952818181818184</v>
       </c>
       <c r="G114">
         <v>1.54E-2</v>
@@ -5968,7 +6076,7 @@
         <v>2.0359829999999999E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>41791</v>
       </c>
@@ -5985,7 +6093,7 @@
         <v>7.5433263114044866</v>
       </c>
       <c r="F115">
-        <v>0.78338566190476211</v>
+        <v>0.78591571428571427</v>
       </c>
       <c r="G115">
         <v>1.4423809523809525E-2</v>
@@ -6024,7 +6132,7 @@
         <v>-2.44377E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>41821</v>
       </c>
@@ -6041,7 +6149,7 @@
         <v>7.5274711814561996</v>
       </c>
       <c r="F116">
-        <v>0.84515209565217408</v>
+        <v>0.84446347826086943</v>
       </c>
       <c r="G116">
         <v>1.4547826086956522E-2</v>
@@ -6080,7 +6188,7 @@
         <v>6.5617620000000002E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>41852</v>
       </c>
@@ -6097,7 +6205,7 @@
         <v>7.5491195716389727</v>
       </c>
       <c r="F117">
-        <v>0.8401189714285715</v>
+        <v>0.83705190476190472</v>
       </c>
       <c r="G117">
         <v>1.5357142857142859E-2</v>
@@ -6136,7 +6244,7 @@
         <v>5.6788930000000001E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>41883</v>
       </c>
@@ -6153,7 +6261,7 @@
         <v>7.586468793544479</v>
       </c>
       <c r="F118">
-        <v>0.8882499318181819</v>
+        <v>0.88863409090909107</v>
       </c>
       <c r="G118">
         <v>1.519090909090909E-2</v>
@@ -6192,7 +6300,7 @@
         <v>9.1799199999999994E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>41913</v>
       </c>
@@ -6209,7 +6317,7 @@
         <v>7.6241452411474491</v>
       </c>
       <c r="F119">
-        <v>0.96079560869565195</v>
+        <v>0.9707021739130437</v>
       </c>
       <c r="G119">
         <v>1.7417391304347826E-2</v>
@@ -6248,7 +6356,7 @@
         <v>-2.3993029999999999E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>41944</v>
       </c>
@@ -6265,7 +6373,7 @@
         <v>7.662585344729667</v>
       </c>
       <c r="F120">
-        <v>0.98796994500000013</v>
+        <v>0.99695799999999968</v>
       </c>
       <c r="G120">
         <v>1.728E-2</v>
@@ -6304,7 +6412,7 @@
         <v>5.1557000000000003E-4</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>41974</v>
       </c>
@@ -6321,7 +6429,7 @@
         <v>7.7597122687500635</v>
       </c>
       <c r="F121">
-        <v>1.3446652173913043</v>
+        <v>1.3510795652173913</v>
       </c>
       <c r="G121">
         <v>1.9973913043478259E-2</v>
@@ -6360,7 +6468,7 @@
         <v>-5.0954909999999999E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>42005</v>
       </c>
@@ -6377,7 +6485,7 @@
         <v>7.7822610528354756</v>
       </c>
       <c r="F122">
-        <v>1.6627480909090908</v>
+        <v>1.6761059090909092</v>
       </c>
       <c r="G122">
         <v>2.2950000000000002E-2</v>
@@ -6416,7 +6524,7 @@
         <v>2.9688499999999999E-3</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>42036</v>
       </c>
@@ -6433,7 +6541,7 @@
         <v>7.7916798316170182</v>
       </c>
       <c r="F123">
-        <v>1.4222650000000001</v>
+        <v>1.4415895000000001</v>
       </c>
       <c r="G123">
         <v>2.0774999999999998E-2</v>
@@ -6472,7 +6580,7 @@
         <v>2.5778999999999998E-4</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>42064</v>
       </c>
@@ -6489,7 +6597,7 @@
         <v>7.8580918187932056</v>
       </c>
       <c r="F124">
-        <v>1.5822181818181817</v>
+        <v>1.58958</v>
       </c>
       <c r="G124">
         <v>2.2186363636363636E-2</v>
@@ -6528,7 +6636,7 @@
         <v>-4.95328E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>42095</v>
       </c>
@@ -6545,7 +6653,7 @@
         <v>7.8221882863541783</v>
       </c>
       <c r="F125">
-        <v>1.441445454545454</v>
+        <v>1.4568672727272727</v>
       </c>
       <c r="G125">
         <v>2.1572727272727271E-2</v>
@@ -6584,7 +6692,7 @@
         <v>1.403975E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>42125</v>
       </c>
@@ -6601,7 +6709,7 @@
         <v>7.799380297904122</v>
       </c>
       <c r="F126">
-        <v>1.4280142857142861</v>
+        <v>1.4363780952380953</v>
       </c>
       <c r="G126">
         <v>2.0895238095238095E-2</v>
@@ -6640,7 +6748,7 @@
         <v>-2.181311E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>42156</v>
       </c>
@@ -6657,7 +6765,7 @@
         <v>7.8457840189961168</v>
       </c>
       <c r="F127">
-        <v>1.6130136363636365</v>
+        <v>1.6163790909090912</v>
       </c>
       <c r="G127">
         <v>2.2486363636363638E-2</v>
@@ -6696,7 +6804,7 @@
         <v>-1.069549E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>42186</v>
       </c>
@@ -6713,7 +6821,7 @@
         <v>7.9127526167996827</v>
       </c>
       <c r="F128">
-        <v>1.7343869565217389</v>
+        <v>1.7454747826086956</v>
       </c>
       <c r="G128">
         <v>2.4199999999999999E-2</v>
@@ -6752,7 +6860,7 @@
         <v>7.4930300000000003E-3</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>42217</v>
       </c>
@@ -6769,7 +6877,7 @@
         <v>8.0141009213725329</v>
       </c>
       <c r="F129">
-        <v>2.0639190476190477</v>
+        <v>2.0581557142857143</v>
       </c>
       <c r="G129">
         <v>2.7571428571428573E-2</v>
@@ -6808,7 +6916,7 @@
         <v>-5.9726639999999998E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>42248</v>
       </c>
@@ -6825,7 +6933,7 @@
         <v>8.0304486111565421</v>
       </c>
       <c r="F130">
-        <v>2.2183044545454549</v>
+        <v>2.2494622727272731</v>
       </c>
       <c r="G130">
         <v>2.9072727272727274E-2</v>
@@ -6864,7 +6972,7 @@
         <v>7.5437699999999996E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>42278</v>
       </c>
@@ -6881,7 +6989,7 @@
         <v>7.9854333002909135</v>
       </c>
       <c r="F131">
-        <v>2.1979723636363637</v>
+        <v>2.2145095454545451</v>
       </c>
       <c r="G131">
         <v>2.8245454545454542E-2</v>
@@ -6920,7 +7028,7 @@
         <v>8.803975E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>42309</v>
       </c>
@@ -6937,7 +7045,7 @@
         <v>8.0052569511439895</v>
       </c>
       <c r="F132">
-        <v>2.1052329047619045</v>
+        <v>2.1202266666666665</v>
       </c>
       <c r="G132">
         <v>2.803809523809524E-2</v>
@@ -6976,7 +7084,7 @@
         <v>-7.4226639999999997E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>42339</v>
       </c>
@@ -6993,7 +7101,7 @@
         <v>8.0847196161954784</v>
       </c>
       <c r="F133">
-        <v>2.3903128695652178</v>
+        <v>2.412944347826087</v>
       </c>
       <c r="G133">
         <v>3.1373913043478259E-2</v>
@@ -7032,7 +7140,7 @@
         <v>-3.927336E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>42370</v>
       </c>
@@ -7049,7 +7157,7 @@
         <v>8.0968266057315681</v>
       </c>
       <c r="F134">
-        <v>2.7555849047619052</v>
+        <v>2.7749576190476186</v>
       </c>
       <c r="G134">
         <v>3.6742857142857147E-2</v>
@@ -7088,7 +7196,7 @@
         <v>-4.3242210000000003E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>42401</v>
       </c>
@@ -7105,7 +7213,7 @@
         <v>8.1189519283973919</v>
       </c>
       <c r="F135">
-        <v>2.8933274761904766</v>
+        <v>2.9384785714285715</v>
       </c>
       <c r="G135">
         <v>3.9319047619047622E-2</v>
@@ -7144,7 +7252,7 @@
         <v>-4.5211069999999999E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>42430</v>
       </c>
@@ -7161,7 +7269,7 @@
         <v>8.0536518366236898</v>
       </c>
       <c r="F136">
-        <v>2.2438216521739132</v>
+        <v>2.2928769565217393</v>
       </c>
       <c r="G136">
         <v>3.0930434782608693E-2</v>
@@ -7200,7 +7308,7 @@
         <v>2.9679919999999999E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>42461</v>
       </c>
@@ -7217,7 +7325,7 @@
         <v>8.0059374751737362</v>
       </c>
       <c r="F137">
-        <v>2.1656285714285719</v>
+        <v>2.207938571428572</v>
       </c>
       <c r="G137">
         <v>2.868095238095238E-2</v>
@@ -7256,7 +7364,7 @@
         <v>0.10966434</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>42491</v>
       </c>
@@ -7273,7 +7381,7 @@
         <v>8.0024867135347453</v>
       </c>
       <c r="F138">
-        <v>2.2749954545454547</v>
+        <v>2.3029472727272728</v>
       </c>
       <c r="G138">
         <v>2.9122727272727276E-2</v>
@@ -7312,7 +7420,7 @@
         <v>-1.8288929999999998E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>42522</v>
       </c>
@@ -7329,7 +7437,7 @@
         <v>8.003590381502951</v>
       </c>
       <c r="F139">
-        <v>2.1981454545454544</v>
+        <v>2.2337986363636362</v>
       </c>
       <c r="G139">
         <v>2.8077272727272725E-2</v>
@@ -7368,7 +7476,7 @@
         <v>-5.4844300000000002E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>42552</v>
       </c>
@@ -7385,7 +7493,7 @@
         <v>7.9942916125911232</v>
       </c>
       <c r="F140">
-        <v>1.8986239523809523</v>
+        <v>1.9198976190476191</v>
       </c>
       <c r="G140">
         <v>2.4980952380952378E-2</v>
@@ -7424,7 +7532,7 @@
         <v>-6.5172099999999998E-3</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>42583</v>
       </c>
@@ -7441,7 +7549,7 @@
         <v>7.9942342558269734</v>
       </c>
       <c r="F141">
-        <v>1.7310434782608695</v>
+        <v>1.7557056521739132</v>
       </c>
       <c r="G141">
         <v>2.341304347826087E-2</v>
@@ -7480,7 +7588,7 @@
         <v>-5.7133200000000002E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>42614</v>
       </c>
@@ -7497,7 +7605,7 @@
         <v>7.9797326533458754</v>
       </c>
       <c r="F142">
-        <v>1.6712818181818181</v>
+        <v>1.6925004545454547</v>
       </c>
       <c r="G142">
         <v>2.3145454545454545E-2</v>
@@ -7536,7 +7644,7 @@
         <v>-2.4688499999999999E-3</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>42644</v>
       </c>
@@ -7553,7 +7661,7 @@
         <v>7.9836480904805596</v>
       </c>
       <c r="F143">
-        <v>1.7257333333333329</v>
+        <v>1.7469676190476191</v>
       </c>
       <c r="G143">
         <v>2.291904761904762E-2</v>
@@ -7592,7 +7700,7 @@
         <v>1.5155699999999999E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>42675</v>
       </c>
@@ -7609,7 +7717,7 @@
         <v>8.0412197784174584</v>
       </c>
       <c r="F144">
-        <v>1.919981818181818</v>
+        <v>1.9400822727272731</v>
       </c>
       <c r="G144">
         <v>2.5177272727272729E-2</v>
@@ -7648,7 +7756,7 @@
         <v>4.7110700000000004E-3</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>42705</v>
       </c>
@@ -7665,7 +7773,7 @@
         <v>8.0095391993714351</v>
       </c>
       <c r="F145">
-        <v>1.6780590909090913</v>
+        <v>1.6995213636363631</v>
       </c>
       <c r="G145">
         <v>2.2763636363636361E-2</v>
@@ -7704,7 +7812,7 @@
         <v>-0.10871107000000001</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>42736</v>
       </c>
@@ -7721,7 +7829,7 @@
         <v>7.9877452435221521</v>
       </c>
       <c r="F146">
-        <v>1.5281272727272723</v>
+        <v>1.5440331818181823</v>
       </c>
       <c r="G146">
         <v>2.1136363636363637E-2</v>
@@ -7760,7 +7868,7 @@
         <v>9.5875409999999994E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>42767</v>
       </c>
@@ -7777,7 +7885,7 @@
         <v>7.966128736390572</v>
       </c>
       <c r="F147">
-        <v>1.4152900000000002</v>
+        <v>1.4274264999999999</v>
       </c>
       <c r="G147">
         <v>1.9915000000000002E-2</v>
@@ -7816,7 +7924,7 @@
         <v>-7.9695489999999994E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>42795</v>
       </c>
@@ -7833,7 +7941,7 @@
         <v>7.987351231146425</v>
       </c>
       <c r="F148">
-        <v>1.3559869565217391</v>
+        <v>1.3647273913043476</v>
       </c>
       <c r="G148">
         <v>1.9508695652173912E-2</v>
@@ -7872,7 +7980,7 @@
         <v>4.9257790000000003E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>42826</v>
       </c>
@@ -7889,7 +7997,7 @@
         <v>7.9633034781792196</v>
       </c>
       <c r="F149">
-        <v>1.3230950000000001</v>
+        <v>1.3304339999999999</v>
       </c>
       <c r="G149">
         <v>1.967E-2</v>
@@ -7928,7 +8036,7 @@
         <v>-2.814877E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>42856</v>
       </c>
@@ -7945,7 +8053,7 @@
         <v>7.9807078208696689</v>
       </c>
       <c r="F150">
-        <v>1.2681217391304347</v>
+        <v>1.2742652173913043</v>
       </c>
       <c r="G150">
         <v>1.9456521739130435E-2</v>
@@ -7984,7 +8092,7 @@
         <v>4.8757790000000002E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>42887</v>
       </c>
@@ -8001,7 +8109,7 @@
         <v>7.9923903397193872</v>
       </c>
       <c r="F151">
-        <v>1.2903227272727269</v>
+        <v>1.2935045454545453</v>
       </c>
       <c r="G151">
         <v>1.9636363636363636E-2</v>
@@ -8040,7 +8148,7 @@
         <v>-2.2313110000000001E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>42917</v>
       </c>
@@ -8057,7 +8165,7 @@
         <v>8.0192048164517384</v>
       </c>
       <c r="F152">
-        <v>1.3460190476190474</v>
+        <v>1.3504223809523808</v>
       </c>
       <c r="G152">
         <v>2.000952380952381E-2</v>
@@ -8096,7 +8204,7 @@
         <v>3.5015570000000003E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>42948</v>
       </c>
@@ -8113,7 +8221,7 @@
         <v>7.9971989978089608</v>
       </c>
       <c r="F153">
-        <v>1.2671869565217393</v>
+        <v>1.2693152173913043</v>
       </c>
       <c r="G153">
         <v>2.0069565217391304E-2</v>
@@ -8152,7 +8260,7 @@
         <v>1.6726640000000001E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>42979</v>
       </c>
@@ -8169,7 +8277,7 @@
         <v>7.9788216382202952</v>
       </c>
       <c r="F154">
-        <v>1.1865142857142856</v>
+        <v>1.195931904761905</v>
       </c>
       <c r="G154">
         <v>1.891904761904762E-2</v>
@@ -8208,7 +8316,7 @@
         <v>3.7211069999999999E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>43009</v>
       </c>
@@ -8225,7 +8333,7 @@
         <v>7.9912742342025913</v>
       </c>
       <c r="F155">
-        <v>1.1423909090909092</v>
+        <v>1.1425854545454543</v>
       </c>
       <c r="G155">
         <v>1.8536363636363639E-2</v>
@@ -8264,7 +8372,7 @@
         <v>-0.10117992000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>43040</v>
       </c>
@@ -8281,7 +8389,7 @@
         <v>8.0107479597092244</v>
       </c>
       <c r="F156">
-        <v>1.1699227272727275</v>
+        <v>1.1724695454545455</v>
       </c>
       <c r="G156">
         <v>1.8613636363636363E-2</v>
@@ -8320,7 +8428,7 @@
         <v>-3.2179920000000001E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>43070</v>
       </c>
@@ -8337,7 +8445,7 @@
         <v>8.0035034700355965</v>
       </c>
       <c r="F157">
-        <v>1.0837238095238098</v>
+        <v>1.0841714285714283</v>
       </c>
       <c r="G157">
         <v>1.7328571428571429E-2</v>
@@ -8376,7 +8484,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>43101</v>
       </c>
@@ -8393,7 +8501,7 @@
         <v>7.9612586194832868</v>
       </c>
       <c r="F158">
-        <v>0.93285210869565249</v>
+        <v>0.9367547826086956</v>
       </c>
       <c r="G158">
         <v>1.5991304347826089E-2</v>
@@ -8432,7 +8540,7 @@
         <v>-6.0288929999999998E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>43132</v>
       </c>
@@ -8449,7 +8557,7 @@
         <v>7.9585769038138983</v>
       </c>
       <c r="F159">
-        <v>0.99970996500000009</v>
+        <v>1.0043690000000001</v>
       </c>
       <c r="G159">
         <v>1.729E-2</v>
@@ -8488,7 +8596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>43160</v>
       </c>
@@ -8505,7 +8613,7 @@
         <v>7.955937058850882</v>
       </c>
       <c r="F160">
-        <v>1.0350908909090912</v>
+        <v>1.0367831818181816</v>
       </c>
       <c r="G160">
         <v>1.7890909090909089E-2</v>
@@ -8544,7 +8652,7 @@
         <v>3.2515570000000001E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>43191</v>
       </c>
@@ -8561,7 +8669,7 @@
         <v>7.9251430508041576</v>
       </c>
       <c r="F161">
-        <v>1.0230523571428569</v>
+        <v>1.0230904761904762</v>
       </c>
       <c r="G161">
         <v>1.7328571428571429E-2</v>
@@ -8600,7 +8708,7 @@
         <v>1.4532799999999999E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>43221</v>
       </c>
@@ -8617,7 +8725,7 @@
         <v>7.9596078407472204</v>
       </c>
       <c r="F162">
-        <v>1.1226826086956521</v>
+        <v>1.1225073913043477</v>
       </c>
       <c r="G162">
         <v>1.8991304347826088E-2</v>
@@ -8656,7 +8764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>43252</v>
       </c>
@@ -8673,7 +8781,7 @@
         <v>7.9701253477121892</v>
       </c>
       <c r="F163">
-        <v>1.2350571428571431</v>
+        <v>1.243502857142857</v>
       </c>
       <c r="G163">
         <v>1.9971428571428571E-2</v>
@@ -8712,7 +8820,7 @@
         <v>-1.808647E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>43282</v>
       </c>
@@ -8729,7 +8837,7 @@
         <v>7.9674708020203004</v>
       </c>
       <c r="F164">
-        <v>1.0974909090909089</v>
+        <v>1.1036886363636362</v>
       </c>
       <c r="G164">
         <v>1.8077272727272727E-2</v>
@@ -8768,7 +8876,7 @@
         <v>-2.152418E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>43313</v>
       </c>
@@ -8785,7 +8893,7 @@
         <v>7.992799266495088</v>
       </c>
       <c r="F165">
-        <v>1.0866652173913047</v>
+        <v>1.0897604347826084</v>
       </c>
       <c r="G165">
         <v>1.8239130434782608E-2</v>
@@ -8824,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>43344</v>
       </c>
@@ -8841,7 +8949,7 @@
         <v>8.0188888482039182</v>
       </c>
       <c r="F166">
-        <v>1.1054250000000001</v>
+        <v>1.114749</v>
       </c>
       <c r="G166">
         <v>1.7705000000000002E-2</v>
@@ -8880,7 +8988,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>43374</v>
       </c>
@@ -8897,7 +9005,7 @@
         <v>8.0328407079810251</v>
       </c>
       <c r="F167">
-        <v>1.2018913043478263</v>
+        <v>1.2152669565217389</v>
       </c>
       <c r="G167">
         <v>1.7908695652173911E-2</v>
@@ -8936,7 +9044,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>43405</v>
       </c>
@@ -8953,7 +9061,7 @@
         <v>8.0703215429741988</v>
       </c>
       <c r="F168">
-        <v>1.3125909090909089</v>
+        <v>1.3216890909090908</v>
       </c>
       <c r="G168">
         <v>2.0177272727272728E-2</v>
@@ -8992,7 +9100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>43435</v>
       </c>
@@ -9009,7 +9117,7 @@
         <v>8.0747985035031622</v>
       </c>
       <c r="F169">
-        <v>1.426233333333333</v>
+        <v>1.4346290476190475</v>
       </c>
       <c r="G169">
         <v>2.118095238095238E-2</v>
@@ -9048,7 +9156,7 @@
         <v>5.9377039999999999E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>43466</v>
       </c>
@@ -9065,7 +9173,7 @@
         <v>8.0589315543662359</v>
       </c>
       <c r="F170">
-        <v>1.3404999999999998</v>
+        <v>1.3506604347826086</v>
       </c>
       <c r="G170">
         <v>2.0143478260869565E-2</v>
@@ -9104,7 +9212,7 @@
         <v>1.0390979999999999E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>43497</v>
       </c>
@@ -9121,7 +9229,7 @@
         <v>8.0440325841552802</v>
       </c>
       <c r="F171">
-        <v>1.1630799999999999</v>
+        <v>1.1653710000000004</v>
       </c>
       <c r="G171">
         <v>1.9099999999999999E-2</v>
@@ -9160,7 +9268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>43525</v>
       </c>
@@ -9177,7 +9285,7 @@
         <v>8.0472983562522113</v>
       </c>
       <c r="F172">
-        <v>1.1016761904761907</v>
+        <v>1.1043176190476189</v>
       </c>
       <c r="G172">
         <v>1.8814285714285714E-2</v>
@@ -9216,7 +9324,7 @@
         <v>-6.1799200000000002E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>43556</v>
       </c>
@@ -9233,7 +9341,7 @@
         <v>8.0568135031306198</v>
       </c>
       <c r="F173">
-        <v>0.99575903636363639</v>
+        <v>1.0006295454545453</v>
       </c>
       <c r="G173">
         <v>1.7695454545454545E-2</v>
@@ -9272,7 +9380,7 @@
         <v>9.6487699999999992E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>43586</v>
       </c>
@@ -9289,7 +9397,7 @@
         <v>8.1048514936685994</v>
       </c>
       <c r="F174">
-        <v>1.0853652086956522</v>
+        <v>1.0859226086956522</v>
       </c>
       <c r="G174">
         <v>1.9060869565217391E-2</v>
@@ -9328,7 +9436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>43617</v>
       </c>
@@ -9345,7 +9453,7 @@
         <v>8.0882608696097087</v>
       </c>
       <c r="F175">
-        <v>1.026514975</v>
+        <v>1.0298185</v>
       </c>
       <c r="G175">
         <v>1.8960000000000001E-2</v>
@@ -9384,7 +9492,7 @@
         <v>8.6799200000000007E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>43647</v>
       </c>
@@ -9401,7 +9509,7 @@
         <v>8.0734372576753497</v>
       </c>
       <c r="F176">
-        <v>0.85816514782608677</v>
+        <v>0.8555960869565219</v>
       </c>
       <c r="G176">
         <v>1.7247826086956523E-2</v>
@@ -9440,7 +9548,7 @@
         <v>5.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>43678</v>
       </c>
@@ -9457,7 +9565,7 @@
         <v>8.1352443945711332</v>
       </c>
       <c r="F177">
-        <v>0.98422723636363629</v>
+        <v>0.98437499999999989</v>
       </c>
       <c r="G177">
         <v>1.8736363636363638E-2</v>
@@ -9496,7 +9604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>43709</v>
       </c>
@@ -9513,7 +9621,7 @@
         <v>8.1314189396522298</v>
       </c>
       <c r="F178">
-        <v>0.86393801904761924</v>
+        <v>0.85993761904761912</v>
       </c>
       <c r="G178">
         <v>1.7590476190476191E-2</v>
@@ -9552,7 +9660,7 @@
         <v>2.4221E-4</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>43739</v>
       </c>
@@ -9569,7 +9677,7 @@
         <v>8.1425666488274224</v>
       </c>
       <c r="F179">
-        <v>0.87718689565217389</v>
+        <v>0.87405173913043444</v>
       </c>
       <c r="G179">
         <v>1.7860869565217392E-2</v>
@@ -9608,7 +9716,7 @@
         <v>9.2761060000000006E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>43770</v>
       </c>
@@ -9625,7 +9733,7 @@
         <v>8.1348839058852551</v>
       </c>
       <c r="F180">
-        <v>0.833004680952381</v>
+        <v>0.83028666666666662</v>
       </c>
       <c r="G180">
         <v>1.8185714285714288E-2</v>
@@ -9664,7 +9772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>43800</v>
       </c>
@@ -9681,7 +9789,7 @@
         <v>8.1265181687807093</v>
       </c>
       <c r="F181">
-        <v>0.77261356818181826</v>
+        <v>0.77088136363636339</v>
       </c>
       <c r="G181">
         <v>1.7104545454545452E-2</v>

--- a/R/Input/DATAccorta.xlsx
+++ b/R/Input/DATAccorta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bancodelarepublica-my.sharepoint.com/personal/ojaulime_banrep_gov_co/Documents/Documents/Research/MP transmission in Colombia/Monetary-Policy-Shocks-and-Central-bank-information-in-Colombia/R/Input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disco C\Repositorios Git\Monetary-Policy-Shocks-and-Central-bank-information-in-Colombia\R\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{61A7BA06-15EE-486E-B896-9040FC5EED2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4FA15D0-B2B8-497B-A00F-A9EB71660AB7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC033C0C-2273-45E2-9F60-E85AC5674B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5935AB3E-80CE-4E87-9EB4-B18D2E64BDED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5935AB3E-80CE-4E87-9EB4-B18D2E64BDED}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -54,18 +54,6 @@
     <t>ShockOISL</t>
   </si>
   <si>
-    <t>MP_bloomberg</t>
-  </si>
-  <si>
-    <t>CBI_bloomberg</t>
-  </si>
-  <si>
-    <t>MP_OIS</t>
-  </si>
-  <si>
-    <t>CBI_OIS</t>
-  </si>
-  <si>
     <t>MP_bloo_BEI</t>
   </si>
   <si>
@@ -85,6 +73,18 @@
   </si>
   <si>
     <t>EMBIL</t>
+  </si>
+  <si>
+    <t>MP_OIS_colcap</t>
+  </si>
+  <si>
+    <t>CBI_OIS_colcap</t>
+  </si>
+  <si>
+    <t>MP_bloo_colcap</t>
+  </si>
+  <si>
+    <t>CBI_bloo_colcap</t>
   </si>
 </sst>
 </file>
@@ -139,10 +139,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -443,9 +439,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11DADDA8-F05A-4B81-9CDB-818A1AD50DCA}">
   <dimension ref="A1:Q181"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -459,13 +455,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H1" t="s">
         <v>4</v>
@@ -474,31 +470,31 @@
         <v>5</v>
       </c>
       <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="Q1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>38353</v>
       </c>
@@ -527,7 +523,7 @@
         <v>4.5591700000000004E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>38384</v>
       </c>
@@ -556,7 +552,7 @@
         <v>1.36775E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>38412</v>
       </c>
@@ -585,7 +581,7 @@
         <v>0.11486080999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>38443</v>
       </c>
@@ -614,7 +610,7 @@
         <v>5.4710000000000002E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>38473</v>
       </c>
@@ -643,7 +639,7 @@
         <v>2.2645E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>38504</v>
       </c>
@@ -672,7 +668,7 @@
         <v>-5.5011599999999997E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>38534</v>
       </c>
@@ -701,7 +697,7 @@
         <v>-2.826683E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>38565</v>
       </c>
@@ -730,7 +726,7 @@
         <v>4.5592000000000001E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>38596</v>
       </c>
@@ -759,7 +755,7 @@
         <v>-0.23819141999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>38626</v>
       </c>
@@ -788,7 +784,7 @@
         <v>2.860209E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>38657</v>
       </c>
@@ -817,7 +813,7 @@
         <v>-1.8236699999999999E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>38687</v>
       </c>
@@ -846,7 +842,7 @@
         <v>3.1914159999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>38718</v>
       </c>
@@ -875,7 +871,7 @@
         <v>3.1914199999999999E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>38749</v>
       </c>
@@ -904,7 +900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>38777</v>
       </c>
@@ -933,7 +929,7 @@
         <v>5.9269199999999996E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>38808</v>
       </c>
@@ -962,7 +958,7 @@
         <v>7.2976819999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>38838</v>
       </c>
@@ -991,7 +987,7 @@
         <v>-0.11150349</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>38869</v>
       </c>
@@ -1020,7 +1016,7 @@
         <v>1.5440829999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>38899</v>
       </c>
@@ -1049,7 +1045,7 @@
         <v>-9.8828319999999997E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>38930</v>
       </c>
@@ -1078,7 +1074,7 @@
         <v>8.6171700000000004E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>38961</v>
       </c>
@@ -1107,7 +1103,7 @@
         <v>7.2720419999999994E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>38991</v>
       </c>
@@ -1136,7 +1132,7 @@
         <v>5.8236660000000003E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>39022</v>
       </c>
@@ -1165,7 +1161,7 @@
         <v>-2.591183E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>39052</v>
       </c>
@@ -1194,7 +1190,7 @@
         <v>0.10091182999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>39083</v>
       </c>
@@ -1223,7 +1219,7 @@
         <v>2.305567E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>39114</v>
       </c>
@@ -1252,7 +1248,7 @@
         <v>-0.11212531000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>39142</v>
       </c>
@@ -1281,7 +1277,7 @@
         <v>-3.2370080000000002E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>39173</v>
       </c>
@@ -1310,7 +1306,7 @@
         <v>-4.529E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>39203</v>
       </c>
@@ -1339,7 +1335,7 @@
         <v>-0.23709169999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>39234</v>
       </c>
@@ -1368,7 +1364,7 @@
         <v>-5.8933899999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>39264</v>
       </c>
@@ -1397,7 +1393,7 @@
         <v>5.5911830000000003E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>39295</v>
       </c>
@@ -1426,7 +1422,7 @@
         <v>-5.674825E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>39326</v>
       </c>
@@ -1455,7 +1451,7 @@
         <v>-0.23797336999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>39356</v>
       </c>
@@ -1484,7 +1480,7 @@
         <v>-0.25985736999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>39387</v>
       </c>
@@ -1513,7 +1509,7 @@
         <v>0.11908816999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>39417</v>
       </c>
@@ -1542,7 +1538,7 @@
         <v>0.23253254000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>39448</v>
       </c>
@@ -1595,7 +1591,7 @@
         <v>-4.2562299999999997E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>39479</v>
       </c>
@@ -1648,7 +1644,7 @@
         <v>5.9226639999999997E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39508</v>
       </c>
@@ -1701,7 +1697,7 @@
         <v>0.32610652000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39539</v>
       </c>
@@ -1754,7 +1750,7 @@
         <v>0.36944381999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>39569</v>
       </c>
@@ -1807,7 +1803,7 @@
         <v>-0.44944381999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>39600</v>
       </c>
@@ -1860,7 +1856,7 @@
         <v>-0.44350611000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>39630</v>
       </c>
@@ -1913,7 +1909,7 @@
         <v>0.46301308000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>39661</v>
       </c>
@@ -1966,7 +1962,7 @@
         <v>-4.4953279999999998E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>39692</v>
       </c>
@@ -2019,7 +2015,7 @@
         <v>-6.0536899999999996E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>39722</v>
       </c>
@@ -2072,7 +2068,7 @@
         <v>-0.49770323999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>39753</v>
       </c>
@@ -2125,7 +2121,7 @@
         <v>-0.38327783999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>39783</v>
       </c>
@@ -2178,7 +2174,7 @@
         <v>0.15606513999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>39814</v>
       </c>
@@ -2231,7 +2227,7 @@
         <v>-0.47338358000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>39845</v>
       </c>
@@ -2284,7 +2280,7 @@
         <v>-0.54739097999999997</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>39873</v>
       </c>
@@ -2337,7 +2333,7 @@
         <v>-0.51314877000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>39904</v>
       </c>
@@ -2390,7 +2386,7 @@
         <v>-0.55107950000000006</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>39934</v>
       </c>
@@ -2443,7 +2439,7 @@
         <v>-0.50324221000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>39965</v>
       </c>
@@ -2496,7 +2492,7 @@
         <v>-0.63880201999999997</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>39995</v>
       </c>
@@ -2549,7 +2545,7 @@
         <v>1.3102050000000001E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>40026</v>
       </c>
@@ -2602,7 +2598,7 @@
         <v>6.4171309999999995E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>40057</v>
       </c>
@@ -2655,7 +2651,7 @@
         <v>-0.24067295</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>40087</v>
       </c>
@@ -2708,7 +2704,7 @@
         <v>-1.2484429999999999E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>40118</v>
       </c>
@@ -2761,7 +2757,7 @@
         <v>-0.35513646999999998</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>40148</v>
       </c>
@@ -2814,7 +2810,7 @@
         <v>0.12279754</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>40179</v>
       </c>
@@ -2867,7 +2863,7 @@
         <v>0.11314877</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>40210</v>
       </c>
@@ -2920,7 +2916,7 @@
         <v>0.10201721</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>40238</v>
       </c>
@@ -2973,7 +2969,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>40269</v>
       </c>
@@ -3026,7 +3022,7 @@
         <v>-0.27829754000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>40299</v>
       </c>
@@ -3079,7 +3075,7 @@
         <v>-3.0679919999999999E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>40330</v>
       </c>
@@ -3132,7 +3128,7 @@
         <v>-3.0679919999999999E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>40360</v>
       </c>
@@ -3185,7 +3181,7 @@
         <v>-3.2695490000000001E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>40391</v>
       </c>
@@ -3238,7 +3234,7 @@
         <v>0.19299957000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>40422</v>
       </c>
@@ -3291,7 +3287,7 @@
         <v>-0.15866063999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>40452</v>
       </c>
@@ -3344,7 +3340,7 @@
         <v>-2.303115E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>40483</v>
       </c>
@@ -3397,7 +3393,7 @@
         <v>0.11330941</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>40513</v>
       </c>
@@ -3450,7 +3446,7 @@
         <v>-4.4633199999999998E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>40544</v>
       </c>
@@ -3503,7 +3499,7 @@
         <v>-2.235123E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>40575</v>
       </c>
@@ -3556,7 +3552,7 @@
         <v>9.36332E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>40603</v>
       </c>
@@ -3609,7 +3605,7 @@
         <v>0.24520900000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>40634</v>
       </c>
@@ -3662,7 +3658,7 @@
         <v>2.351557E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>40664</v>
       </c>
@@ -3715,7 +3711,7 @@
         <v>5.9281970000000003E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>40695</v>
       </c>
@@ -3768,7 +3764,7 @@
         <v>6.0484429999999999E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>40725</v>
       </c>
@@ -3821,7 +3817,7 @@
         <v>2.2031149999999999E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>40756</v>
       </c>
@@ -3874,7 +3870,7 @@
         <v>-0.23957581</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>40787</v>
       </c>
@@ -3927,7 +3923,7 @@
         <v>-4.789098E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>40817</v>
       </c>
@@ -3980,7 +3976,7 @@
         <v>-5.9437700000000003E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>40848</v>
       </c>
@@ -4033,7 +4029,7 @@
         <v>4.510902E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>40878</v>
       </c>
@@ -4086,7 +4082,7 @@
         <v>-3.4757789999999997E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>40909</v>
       </c>
@@ -4139,7 +4135,7 @@
         <v>0.11464877</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>40940</v>
       </c>
@@ -4192,7 +4188,7 @@
         <v>8.6711070000000001E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>40969</v>
       </c>
@@ -4245,7 +4241,7 @@
         <v>-1.2164339999999999E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>41000</v>
       </c>
@@ -4298,7 +4294,7 @@
         <v>-1.2437699999999999E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>41030</v>
       </c>
@@ -4351,7 +4347,7 @@
         <v>-0.23711719000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>41061</v>
       </c>
@@ -4404,7 +4400,7 @@
         <v>-2.275779E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>41091</v>
       </c>
@@ -4457,7 +4453,7 @@
         <v>-0.18792212999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>41122</v>
       </c>
@@ -4510,7 +4506,7 @@
         <v>-4.3515570000000003E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>41153</v>
       </c>
@@ -4563,7 +4559,7 @@
         <v>-8.2380309999999998E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>41183</v>
       </c>
@@ -4616,7 +4612,7 @@
         <v>1.7195490000000001E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>41214</v>
       </c>
@@ -4669,7 +4665,7 @@
         <v>-0.22312088999999999</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>41244</v>
       </c>
@@ -4722,7 +4718,7 @@
         <v>-3.877336E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>41275</v>
       </c>
@@ -4775,7 +4771,7 @@
         <v>1.8468849999999998E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>41306</v>
       </c>
@@ -4828,7 +4824,7 @@
         <v>0.12164506999999999</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>41334</v>
       </c>
@@ -4881,7 +4877,7 @@
         <v>-0.24754302</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>41365</v>
       </c>
@@ -4934,7 +4930,7 @@
         <v>0.17684753</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>41395</v>
       </c>
@@ -4987,7 +4983,7 @@
         <v>0.16510695</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>41426</v>
       </c>
@@ -5040,7 +5036,7 @@
         <v>0.20424875000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>41456</v>
       </c>
@@ -5093,7 +5089,7 @@
         <v>0.14866925</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>41487</v>
       </c>
@@ -5146,7 +5142,7 @@
         <v>-0.14827826999999999</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>41518</v>
       </c>
@@ -5199,7 +5195,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>41548</v>
       </c>
@@ -5252,7 +5248,7 @@
         <v>1.72664E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>41579</v>
       </c>
@@ -5305,7 +5301,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>41609</v>
       </c>
@@ -5358,7 +5354,7 @@
         <v>9.9688499999999996E-3</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>41640</v>
       </c>
@@ -5411,7 +5407,7 @@
         <v>-5.3045100000000001E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>41671</v>
       </c>
@@ -5464,7 +5460,7 @@
         <v>-3.9844299999999997E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>41699</v>
       </c>
@@ -5517,7 +5513,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>41730</v>
       </c>
@@ -5570,7 +5566,7 @@
         <v>0.12378893000000001</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>41760</v>
       </c>
@@ -5623,7 +5619,7 @@
         <v>2.0359829999999999E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>41791</v>
       </c>
@@ -5676,7 +5672,7 @@
         <v>-2.44377E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>41821</v>
       </c>
@@ -5729,7 +5725,7 @@
         <v>6.5617620000000002E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>41852</v>
       </c>
@@ -5782,7 +5778,7 @@
         <v>5.6788930000000001E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>41883</v>
       </c>
@@ -5835,7 +5831,7 @@
         <v>9.1799199999999994E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>41913</v>
       </c>
@@ -5888,7 +5884,7 @@
         <v>-2.3993029999999999E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>41944</v>
       </c>
@@ -5941,7 +5937,7 @@
         <v>5.1557000000000003E-4</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>41974</v>
       </c>
@@ -5994,7 +5990,7 @@
         <v>-5.0954909999999999E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>42005</v>
       </c>
@@ -6047,7 +6043,7 @@
         <v>2.9688499999999999E-3</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>42036</v>
       </c>
@@ -6100,7 +6096,7 @@
         <v>2.5778999999999998E-4</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>42064</v>
       </c>
@@ -6153,7 +6149,7 @@
         <v>-4.95328E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>42095</v>
       </c>
@@ -6206,7 +6202,7 @@
         <v>1.403975E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>42125</v>
       </c>
@@ -6259,7 +6255,7 @@
         <v>-2.181311E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>42156</v>
       </c>
@@ -6312,7 +6308,7 @@
         <v>-1.069549E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>42186</v>
       </c>
@@ -6365,7 +6361,7 @@
         <v>7.4930300000000003E-3</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>42217</v>
       </c>
@@ -6418,7 +6414,7 @@
         <v>-5.9726639999999998E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>42248</v>
       </c>
@@ -6471,7 +6467,7 @@
         <v>7.5437699999999996E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>42278</v>
       </c>
@@ -6524,7 +6520,7 @@
         <v>8.803975E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>42309</v>
       </c>
@@ -6577,7 +6573,7 @@
         <v>-7.4226639999999997E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>42339</v>
       </c>
@@ -6630,7 +6626,7 @@
         <v>-3.927336E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>42370</v>
       </c>
@@ -6683,7 +6679,7 @@
         <v>-4.3242210000000003E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>42401</v>
       </c>
@@ -6736,7 +6732,7 @@
         <v>-4.5211069999999999E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>42430</v>
       </c>
@@ -6789,7 +6785,7 @@
         <v>2.9679919999999999E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>42461</v>
       </c>
@@ -6842,7 +6838,7 @@
         <v>0.10966434</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>42491</v>
       </c>
@@ -6895,7 +6891,7 @@
         <v>-1.8288929999999998E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>42522</v>
       </c>
@@ -6948,7 +6944,7 @@
         <v>-5.4844300000000002E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>42552</v>
       </c>
@@ -7001,7 +6997,7 @@
         <v>-6.5172099999999998E-3</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>42583</v>
       </c>
@@ -7054,7 +7050,7 @@
         <v>-5.7133200000000002E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>42614</v>
       </c>
@@ -7107,7 +7103,7 @@
         <v>-2.4688499999999999E-3</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>42644</v>
       </c>
@@ -7160,7 +7156,7 @@
         <v>1.5155699999999999E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>42675</v>
       </c>
@@ -7213,7 +7209,7 @@
         <v>4.7110700000000004E-3</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>42705</v>
       </c>
@@ -7266,7 +7262,7 @@
         <v>-0.10871107000000001</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>42736</v>
       </c>
@@ -7319,7 +7315,7 @@
         <v>9.5875409999999994E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>42767</v>
       </c>
@@ -7372,7 +7368,7 @@
         <v>-7.9695489999999994E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>42795</v>
       </c>
@@ -7425,7 +7421,7 @@
         <v>4.9257790000000003E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>42826</v>
       </c>
@@ -7478,7 +7474,7 @@
         <v>-2.814877E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>42856</v>
       </c>
@@ -7531,7 +7527,7 @@
         <v>4.8757790000000002E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>42887</v>
       </c>
@@ -7584,7 +7580,7 @@
         <v>-2.2313110000000001E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>42917</v>
       </c>
@@ -7637,7 +7633,7 @@
         <v>3.5015570000000003E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>42948</v>
       </c>
@@ -7690,7 +7686,7 @@
         <v>1.6726640000000001E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>42979</v>
       </c>
@@ -7743,7 +7739,7 @@
         <v>3.7211069999999999E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>43009</v>
       </c>
@@ -7796,7 +7792,7 @@
         <v>-0.10117992000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>43040</v>
       </c>
@@ -7849,7 +7845,7 @@
         <v>-3.2179920000000001E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>43070</v>
       </c>
@@ -7902,7 +7898,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>43101</v>
       </c>
@@ -7955,7 +7951,7 @@
         <v>-6.0288929999999998E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>43132</v>
       </c>
@@ -8008,7 +8004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>43160</v>
       </c>
@@ -8061,7 +8057,7 @@
         <v>3.2515570000000001E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>43191</v>
       </c>
@@ -8114,7 +8110,7 @@
         <v>1.4532799999999999E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>43221</v>
       </c>
@@ -8167,7 +8163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>43252</v>
       </c>
@@ -8220,7 +8216,7 @@
         <v>-1.808647E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>43282</v>
       </c>
@@ -8273,7 +8269,7 @@
         <v>-2.152418E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>43313</v>
       </c>
@@ -8326,7 +8322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>43344</v>
       </c>
@@ -8379,7 +8375,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>43374</v>
       </c>
@@ -8432,7 +8428,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>43405</v>
       </c>
@@ -8485,7 +8481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>43435</v>
       </c>
@@ -8538,7 +8534,7 @@
         <v>5.9377039999999999E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>43466</v>
       </c>
@@ -8591,7 +8587,7 @@
         <v>1.0390979999999999E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>43497</v>
       </c>
@@ -8644,7 +8640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>43525</v>
       </c>
@@ -8697,7 +8693,7 @@
         <v>-6.1799200000000002E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>43556</v>
       </c>
@@ -8750,7 +8746,7 @@
         <v>9.6487699999999992E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>43586</v>
       </c>
@@ -8803,7 +8799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>43617</v>
       </c>
@@ -8856,7 +8852,7 @@
         <v>8.6799200000000007E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>43647</v>
       </c>
@@ -8909,7 +8905,7 @@
         <v>5.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>43678</v>
       </c>
@@ -8962,7 +8958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>43709</v>
       </c>
@@ -9015,7 +9011,7 @@
         <v>2.4221E-4</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>43739</v>
       </c>
@@ -9068,7 +9064,7 @@
         <v>9.2761060000000006E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>43770</v>
       </c>
@@ -9121,7 +9117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>43800</v>
       </c>
